--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104685_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104685_W26.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1787</v>
+        <v>5.1143</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1363</v>
+        <v>4.6059</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0424</v>
+        <v>0.5084</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7959</v>
+        <v>1.7951</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7923</v>
+        <v>-0.7845</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5882</v>
+        <v>2.5796</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8075</v>
+        <v>3.7841</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L2" t="n">
-        <v>3.6862</v>
+        <v>3.6634</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.0116</v>
+        <v>-1.989</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0981</v>
+        <v>-1.0838</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>4.9292</v>
+        <v>2.8639</v>
       </c>
       <c r="T2" t="n">
-        <v>3.6898</v>
+        <v>2.1876</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2394</v>
+        <v>0.6763</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2109</v>
+        <v>4.4497</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0186</v>
+        <v>3.9434</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1923</v>
+        <v>0.5064</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8678</v>
+        <v>3.875</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7358</v>
+        <v>0.7407</v>
       </c>
       <c r="I3" t="n">
-        <v>3.132</v>
+        <v>3.1343</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2394</v>
+        <v>5.219</v>
       </c>
       <c r="K3" t="n">
-        <v>1.697</v>
+        <v>1.6892</v>
       </c>
       <c r="L3" t="n">
-        <v>3.5424</v>
+        <v>3.5298</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3716</v>
+        <v>-1.3441</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4104</v>
+        <v>-0.3956</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0541</v>
+        <v>1.1973</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1966</v>
+        <v>1.1679</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2507</v>
+        <v>0.0294</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4534</v>
+        <v>0.8955</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2206</v>
+        <v>3.3651</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7672</v>
+        <v>-2.4696</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.356</v>
+        <v>-0.0337</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0403</v>
+        <v>-0.0466</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.3963</v>
+        <v>0.0129</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.203</v>
+        <v>2.8288</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6234</v>
+        <v>0.9308</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8264</v>
+        <v>1.898</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.153</v>
+        <v>-2.8624</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5831</v>
+        <v>-0.9774</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5699</v>
+        <v>-1.8851</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6708</v>
+        <v>-0.6156</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6956</v>
+        <v>-0.2769</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0248</v>
+        <v>-0.3388</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3461</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3461</v>
+        <v>2.1789</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3909</v>
+        <v>0.6987</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1511</v>
+        <v>1.5046</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.7602</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.034</v>
+        <v>-2.3465</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0579</v>
+        <v>0.0457</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0239</v>
+        <v>-2.3921</v>
       </c>
       <c r="J5" t="n">
-        <v>2.862</v>
+        <v>-0.214</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9351</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9269</v>
+        <v>-0.8345</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.896</v>
+        <v>-2.1325</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.993</v>
+        <v>-0.5749</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.903</v>
+        <v>-1.5576</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1215</v>
+        <v>-0.4297</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5353</v>
+        <v>-0.3904</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5861</v>
+        <v>-0.0392</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>2.3367</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1853</v>
+        <v>2.3367</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2322</v>
+        <v>-0.6223</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7618</v>
+        <v>-1.2026</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.994</v>
+        <v>0.5803</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0743</v>
+        <v>-1.4233</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4128</v>
+        <v>-0.382</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3384</v>
+        <v>-1.0413</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7456</v>
+        <v>-0.8512999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.0205</v>
       </c>
       <c r="L6" t="n">
-        <v>0.112</v>
+        <v>-0.8718</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6712</v>
+        <v>-0.572</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2209</v>
+        <v>-0.4025</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4504</v>
+        <v>-0.1695</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1983</v>
+        <v>-0.425</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0162</v>
+        <v>-0.4392</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1821</v>
+        <v>0.0141</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1853</v>
+        <v>0.3155</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6484</v>
+        <v>-0.6362</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2418</v>
+        <v>0.2388</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8902</v>
+        <v>-0.875</v>
       </c>
       <c r="G7" t="n">
-        <v>0.287</v>
+        <v>0.2954</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6566</v>
+        <v>-0.6522</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7983</v>
+        <v>0.7964</v>
       </c>
       <c r="K7" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5113</v>
+        <v>-0.5011</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7086</v>
+        <v>-0.7039</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8378</v>
+        <v>0.8408</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8045</v>
+        <v>0.8082</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0333</v>
+        <v>0.0327</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-1.0358</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3676</v>
+        <v>0.9977</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6887</v>
+        <v>-2.0335</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.422</v>
+        <v>0.0793</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3824</v>
+        <v>0.4081</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0396</v>
+        <v>-0.3288</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8362000000000001</v>
+        <v>0.7355</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0275</v>
+        <v>0.6238</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8637</v>
+        <v>0.1117</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5858</v>
+        <v>-0.6562</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4099</v>
+        <v>-0.2157</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1759</v>
+        <v>-0.4405</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4857</v>
+        <v>0.3809</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6261</v>
+        <v>0.2622</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1403</v>
+        <v>0.1187</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3214</v>
+        <v>-2.1789</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>D. RUSSELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8229</v>
+        <v>-1.6504</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4585</v>
+        <v>0.4592</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2814</v>
+        <v>-2.1097</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3482</v>
+        <v>1.6028</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8125</v>
+        <v>-2.1132</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5357</v>
+        <v>3.716</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9938</v>
+        <v>2.0879</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1976</v>
+        <v>-1.5383</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1914</v>
+        <v>3.6262</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.342</v>
+        <v>-0.4851</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6149</v>
+        <v>-0.5749</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7272</v>
+        <v>0.0898</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-2.7316</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8713</v>
+        <v>1.2915</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8257</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0457</v>
+        <v>0.3463</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.7997</v>
+        <v>-2.7237</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7997</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4828</v>
+        <v>-1.7293</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4868</v>
+        <v>-1.8573</v>
       </c>
       <c r="F10" t="n">
-        <v>0.004</v>
+        <v>0.128</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0868</v>
+        <v>-3.0916</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9595</v>
+        <v>0.962</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.0463</v>
+        <v>-4.0536</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5311</v>
+        <v>-1.5619</v>
       </c>
       <c r="K10" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.2628</v>
+        <v>-3.2856</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5557</v>
+        <v>-1.5296</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7835</v>
+        <v>-0.768</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3771</v>
+        <v>1.1346</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4053</v>
+        <v>1.0704</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0281</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. RUSSELL</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0197</v>
+        <v>-2.1659</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6901</v>
+        <v>0.1112</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3296</v>
+        <v>-2.2772</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6282</v>
+        <v>-1.3389</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1007</v>
+        <v>-0.8073</v>
       </c>
       <c r="I11" t="n">
-        <v>3.729</v>
+        <v>-0.5316</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1313</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5177</v>
+        <v>-0.2036</v>
       </c>
       <c r="L11" t="n">
-        <v>3.6489</v>
+        <v>1.1839</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.503</v>
+        <v>-2.3193</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5831</v>
+        <v>-0.6037</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08</v>
+        <v>-1.7155</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.722</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1016</v>
+        <v>0.5097</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2601</v>
+        <v>0.4967</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1585</v>
+        <v>0.013</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.7317</v>
+        <v>-1.792</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8924</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7063</v>
+        <v>-3.6252</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5687</v>
+        <v>-2.5538</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1376</v>
+        <v>-1.0713</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.3629</v>
+        <v>-3.3681</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8094</v>
+        <v>-0.8181</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.5535</v>
+        <v>-2.5501</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3414</v>
+        <v>-0.3767</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1519</v>
+        <v>0.1304</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.0215</v>
+        <v>-2.9915</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.0603</v>
+        <v>-2.043</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6233</v>
+        <v>-0.5239</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2389</v>
+        <v>-0.1677</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3844</v>
+        <v>-0.3562</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3573</v>
+        <v>-0.3068999999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>8.875500000000002</v>
+        <v>9.612200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.2328</v>
+        <v>-9.9191</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.956699999999999</v>
+        <v>-3.9545</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.4634</v>
+        <v>-3.4474</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4930999999999996</v>
+        <v>-0.5070999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>13.6662</v>
+        <v>13.4281</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2581</v>
+        <v>4.1694</v>
       </c>
       <c r="L13" t="n">
-        <v>9.407999999999999</v>
+        <v>9.258699999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-17.6227</v>
+        <v>-17.3828</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.7215</v>
+        <v>-7.6169</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.901400000000001</v>
+        <v>-9.766000000000002</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q13" t="n">
-        <v>-18.1466</v>
+        <v>-18.2106</v>
       </c>
       <c r="R13" t="n">
-        <v>15.8784</v>
+        <v>15.9344</v>
       </c>
       <c r="S13" t="n">
-        <v>5.156699999999999</v>
+        <v>6.2245</v>
       </c>
       <c r="T13" t="n">
-        <v>4.5821</v>
+        <v>5.6639</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5748000000000002</v>
+        <v>0.5605</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2890000000000001</v>
+        <v>-0.3006999999999995</v>
       </c>
       <c r="W13" t="n">
-        <v>8.7737</v>
+        <v>8.730599999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.062799999999999</v>
+        <v>-9.0313</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8419</v>
+        <v>6.6653</v>
       </c>
       <c r="E14" t="n">
-        <v>6.867</v>
+        <v>7.301</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0251</v>
+        <v>-0.6357</v>
       </c>
       <c r="G14" t="n">
-        <v>5.4335</v>
+        <v>5.4396</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0966</v>
+        <v>1.0971</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3369</v>
+        <v>4.3425</v>
       </c>
       <c r="J14" t="n">
-        <v>7.6555</v>
+        <v>7.6241</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2397</v>
+        <v>1.2271</v>
       </c>
       <c r="L14" t="n">
-        <v>6.4158</v>
+        <v>6.3971</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.222</v>
+        <v>-2.1846</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.0789</v>
+        <v>-2.0546</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3382</v>
+        <v>-1.527</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.747</v>
+        <v>-0.2744</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5912</v>
+        <v>-1.2526</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.602</v>
+        <v>3.1947</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5465</v>
+        <v>4.631</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9445</v>
+        <v>-1.4363</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5624</v>
+        <v>2.5547</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5323</v>
+        <v>-0.5423</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0947</v>
+        <v>3.097</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4145</v>
+        <v>3.3817</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0906</v>
+        <v>-0.1109</v>
       </c>
       <c r="L15" t="n">
-        <v>3.5051</v>
+        <v>3.4926</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8521</v>
+        <v>-0.827</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4104</v>
+        <v>-0.3956</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2949</v>
+        <v>0.2938</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0393</v>
+        <v>0.1599</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3342</v>
+        <v>0.1339</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>X. CASTANEDA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4172</v>
+        <v>2.3898</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8254</v>
+        <v>2.1968</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4082</v>
+        <v>0.193</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.623</v>
+        <v>0.9114</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0476</v>
+        <v>-1.3151</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.6707</v>
+        <v>2.2265</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4121</v>
+        <v>1.3399</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0016</v>
+        <v>-0.4244</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4105</v>
+        <v>1.7644</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0352</v>
+        <v>-0.4285</v>
       </c>
       <c r="N16" t="n">
-        <v>0.046</v>
+        <v>-0.8907</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.0812</v>
+        <v>0.4622</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9488</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2937</v>
+        <v>0.2312</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4548</v>
+        <v>-0.3417</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1611</v>
+        <v>0.5729</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9320000000000001</v>
+        <v>1.2472</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>2.3367</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. CASTANEDA</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.993</v>
+        <v>1.2646</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8869</v>
+        <v>2.5063</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1061</v>
+        <v>-1.2417</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9262</v>
+        <v>-0.6067</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3101</v>
+        <v>2.0423</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2363</v>
+        <v>-2.6491</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3706</v>
+        <v>2.3951</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4125</v>
+        <v>1.9855</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7831</v>
+        <v>0.4096</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4444</v>
+        <v>-3.0018</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8976</v>
+        <v>0.0568</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4532</v>
+        <v>-3.0587</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.8211</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>2.9592</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1866</v>
+        <v>-0.8814</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6956</v>
+        <v>0.1599</v>
       </c>
       <c r="U17" t="n">
-        <v>0.509</v>
+        <v>-1.0413</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2534</v>
+        <v>0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3461</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>S. RICE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0209</v>
+        <v>0.5052</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>2.3018</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0209</v>
+        <v>-1.7966</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.8441</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.1752</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.669</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>3.7329</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.4342</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.2987</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-2.8888</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.259</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-2.6298</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.8211</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.9592</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0209</v>
+        <v>-0.9127</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.2929</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0209</v>
+        <v>-0.6198</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. RICE</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0731</v>
+        <v>0.0523</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8596</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9326</v>
+        <v>0.0523</v>
       </c>
       <c r="G19" t="n">
-        <v>0.841</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1746</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6664</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7589</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4431</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>3.3158</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.9179</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2685</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.6494</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9488</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4753</v>
+        <v>0.0523</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7652</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7102000000000001</v>
+        <v>0.0523</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>S. EVANS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1384</v>
+        <v>-0.3485</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4442</v>
+        <v>0.9881</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3058</v>
+        <v>-1.3366</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0926</v>
+        <v>-0.6498</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4213</v>
+        <v>2.3149</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6714</v>
+        <v>-2.9647</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9239</v>
+        <v>1.7652</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1775</v>
+        <v>2.258</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7463</v>
+        <v>-0.4929</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1688</v>
+        <v>-2.415</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7563</v>
+        <v>0.0568</v>
       </c>
       <c r="O20" t="n">
-        <v>0.925</v>
+        <v>-2.4719</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.4952</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>2.5039</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3568</v>
+        <v>-1.3541</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0344</v>
+        <v>-0.0863</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3224</v>
+        <v>-1.2678</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>2.5659</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. EVANS</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3244</v>
+        <v>-0.7491</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4562</v>
+        <v>-1.0497</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7806</v>
+        <v>0.3005</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6415999999999999</v>
+        <v>2.1056</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3145</v>
+        <v>0.4249</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9561</v>
+        <v>1.6807</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8045</v>
+        <v>1.9168</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2685</v>
+        <v>1.1721</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.464</v>
+        <v>0.7447</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4461</v>
+        <v>0.1887</v>
       </c>
       <c r="N21" t="n">
-        <v>0.046</v>
+        <v>-0.7472</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.4921</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4952</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.3464</v>
+        <v>0.7387</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6775</v>
+        <v>0.448</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.6689</v>
+        <v>0.2908</v>
       </c>
       <c r="V21" t="n">
-        <v>2.571</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>2.7317</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4284</v>
+        <v>-2.2948</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8681</v>
+        <v>-2.602</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4398</v>
+        <v>0.3073</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1179</v>
+        <v>1.1164</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0043</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1222</v>
+        <v>1.1248</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8002</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8934</v>
+        <v>0.8823</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3019</v>
+        <v>0.3162</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8147</v>
+        <v>0.9546</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1039</v>
+        <v>0.3992</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7107</v>
+        <v>0.5554</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0294</v>
+        <v>-3.8159</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2157</v>
+        <v>-3.8869</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1863</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.2008</v>
+        <v>-4.2108</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1327</v>
+        <v>-1.1344</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.0681</v>
+        <v>-3.0764</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.5481</v>
+        <v>-3.5662</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.44</v>
+        <v>-0.4449</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.1081</v>
+        <v>-3.1213</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6526</v>
+        <v>-0.6446</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6927</v>
+        <v>-0.6895</v>
       </c>
       <c r="O23" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0139</v>
+        <v>0.2159</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6121</v>
+        <v>0.4879</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.524</v>
+        <v>-3.9319</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6806</v>
+        <v>-2.4673</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8434</v>
+        <v>-1.4646</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.5516</v>
+        <v>-3.55</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3881</v>
+        <v>0.3932</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.9397</v>
+        <v>-3.9432</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.985</v>
+        <v>-2.0072</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.6257</v>
+        <v>-2.6449</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5666</v>
+        <v>-1.5428</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.314</v>
+        <v>-1.2982</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9874</v>
+        <v>-1.411</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6956</v>
+        <v>-0.4601</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2918</v>
+        <v>-0.9509</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.357299999999999</v>
+        <v>2.931699999999997</v>
       </c>
       <c r="E25" t="n">
-        <v>10.233</v>
+        <v>9.919100000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.875499999999999</v>
+        <v>-6.987400000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>3.956600000000001</v>
+        <v>3.954500000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>3.4633</v>
+        <v>3.4474</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4932999999999996</v>
+        <v>0.5071000000000021</v>
       </c>
       <c r="J25" t="n">
-        <v>17.6229</v>
+        <v>17.3825</v>
       </c>
       <c r="K25" t="n">
-        <v>7.721399999999999</v>
+        <v>7.616800000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>9.901499999999999</v>
+        <v>9.7659</v>
       </c>
       <c r="M25" t="n">
-        <v>-13.6662</v>
+        <v>-13.4282</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.2581</v>
+        <v>-4.1695</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.408300000000001</v>
+        <v>-9.258799999999997</v>
       </c>
       <c r="P25" t="n">
-        <v>2.268400000000001</v>
+        <v>2.2765</v>
       </c>
       <c r="Q25" t="n">
-        <v>-15.8785</v>
+        <v>-15.9345</v>
       </c>
       <c r="R25" t="n">
-        <v>18.1465</v>
+        <v>18.2104</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.156600000000001</v>
+        <v>-3.5997</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5745999999999998</v>
+        <v>-0.5604</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.582300000000001</v>
+        <v>-3.0392</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2891999999999997</v>
+        <v>0.3006999999999997</v>
       </c>
       <c r="W25" t="n">
-        <v>9.063000000000001</v>
+        <v>9.0314</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.7738</v>
+        <v>-8.730700000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104685_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104685_W26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-9.0313</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104685_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-8.730700000000001</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
